--- a/data/mywildindia-captions.xlsx
+++ b/data/mywildindia-captions.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="bugyal" sheetId="1" r:id="rId1"/>
+    <sheet name="dibru" sheetId="2" r:id="rId2"/>
+    <sheet name="ghnp" sheetId="3" r:id="rId3"/>
+    <sheet name="jabalpur" sheetId="4" r:id="rId4"/>
+    <sheet name="manas" sheetId="5" r:id="rId5"/>
+    <sheet name="tadoba" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -397,53 +402,360 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>file</v>
+        <v>Photo</v>
       </c>
       <c r="B1" t="str">
-        <v>caption</v>
+        <v>Caption</v>
       </c>
       <c r="C1" t="str">
-        <v>creditImage</v>
-      </c>
-      <c r="D1" t="str">
-        <v>creditName</v>
+        <v>Author</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>images/mywild/IMG_001.jpg</v>
+        <v>bugyal_1.jpeg</v>
       </c>
       <c r="B2" t="str">
-        <v>Caption for IMG_001</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>images/pfp_no_pixel.jpeg</v>
-      </c>
-      <c r="D2" t="str">
-        <v>A. Author</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>images/mywild/IMG_002.jpg</v>
+        <v>bugyal_2.jpeg</v>
       </c>
       <c r="B3" t="str">
-        <v>Caption for IMG_002</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>images/pfp_no_pixel.jpeg</v>
-      </c>
-      <c r="D3" t="str">
-        <v>A. Author</v>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>bugyal_3.jpeg</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>bugyal_4.jpeg</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>bugyal_5.jpeg</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>bugyal_6.jpeg</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>bugyal_7.jpeg</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>bugyal_8.jpeg</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>bugyal_9.jpeg</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Caption</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Author</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dibru_1.png</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dibru_2.png</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Caption</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Author</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>36694727_10215851515831486_2806087659884118016_n.jpg</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Caption</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Author</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>jabalpur_1.jpeg</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>jabalpur_2.jpeg</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>jabalpur_3.jpeg</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>jabalpur_4.jpeg</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>jabalpur_5.jpeg</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>jabalpur_6.jpeg</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Caption</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Author</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Caption</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Author</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>